--- a/artfynd/A 23221-2026 artfynd.xlsx
+++ b/artfynd/A 23221-2026 artfynd.xlsx
@@ -1800,7 +1800,7 @@
         <v>133941656</v>
       </c>
       <c r="B13" t="n">
-        <v>83344</v>
+        <v>83351</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         <v>133941654</v>
       </c>
       <c r="B14" t="n">
-        <v>83344</v>
+        <v>83351</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         <v>133941668</v>
       </c>
       <c r="B15" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         <v>133941784</v>
       </c>
       <c r="B16" t="n">
-        <v>83208</v>
+        <v>83215</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>133941669</v>
       </c>
       <c r="B17" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         <v>133941670</v>
       </c>
       <c r="B18" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         <v>133941785</v>
       </c>
       <c r="B19" t="n">
-        <v>83208</v>
+        <v>83215</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 23221-2026 artfynd.xlsx
+++ b/artfynd/A 23221-2026 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121569692</v>
+        <v>121569685</v>
       </c>
       <c r="B2" t="n">
-        <v>90707</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>645978</v>
+        <v>646203</v>
       </c>
       <c r="R2" t="n">
-        <v>7169870</v>
+        <v>7169713</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121569693</v>
+        <v>121569686</v>
       </c>
       <c r="B3" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>645994</v>
+        <v>646207</v>
       </c>
       <c r="R3" t="n">
-        <v>7169871</v>
+        <v>7169711</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,53 +869,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121569688</v>
+        <v>133941668</v>
       </c>
       <c r="B4" t="n">
-        <v>92018</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91974</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fäboliden, Ly lm</t>
+          <t>Öravan, Ly lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>646103</v>
+        <v>646255</v>
       </c>
       <c r="R4" t="n">
-        <v>7169675</v>
+        <v>7169679</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -949,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -969,27 +954,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Linda Spjut</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Linda Spjut</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121569691</v>
+        <v>133941669</v>
       </c>
       <c r="B5" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91974</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,37 +977,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Fäboliden, Ly lm</t>
+          <t>Öravan, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>646104</v>
+        <v>646227</v>
       </c>
       <c r="R5" t="n">
-        <v>7169762</v>
+        <v>7169691</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1051,12 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,65 +1051,60 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Linda Spjut</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Linda Spjut</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121569690</v>
+        <v>133941670</v>
       </c>
       <c r="B6" t="n">
-        <v>92018</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91974</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Fäboliden, Ly lm</t>
+          <t>Öravan, Ly lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>646104</v>
+        <v>646157</v>
       </c>
       <c r="R6" t="n">
-        <v>7169743</v>
+        <v>7169752</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1153,12 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1173,65 +1148,60 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Linda Spjut</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Linda Spjut</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121569689</v>
+        <v>133941784</v>
       </c>
       <c r="B7" t="n">
-        <v>92030</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83222</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4366</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fäboliden, Ly lm</t>
+          <t>Öravan, Ly lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>646095</v>
+        <v>646177</v>
       </c>
       <c r="R7" t="n">
-        <v>7169705</v>
+        <v>7169660</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1255,12 +1225,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1275,27 +1245,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Linda Spjut</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Linda Spjut</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121569684</v>
+        <v>133941785</v>
       </c>
       <c r="B8" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83222</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1303,37 +1268,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fäboliden, Ly lm</t>
+          <t>Öravan, Ly lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>646230</v>
+        <v>646205</v>
       </c>
       <c r="R8" t="n">
-        <v>7169726</v>
+        <v>7169652</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1357,12 +1322,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1377,27 +1342,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Linda Spjut</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Linda Spjut</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121569685</v>
+        <v>121569688</v>
       </c>
       <c r="B9" t="n">
-        <v>91028</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1405,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>646203</v>
+        <v>646103</v>
       </c>
       <c r="R9" t="n">
-        <v>7169713</v>
+        <v>7169675</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1491,15 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121569686</v>
+        <v>121569690</v>
       </c>
       <c r="B10" t="n">
-        <v>90742</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1507,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>646207</v>
+        <v>646104</v>
       </c>
       <c r="R10" t="n">
-        <v>7169711</v>
+        <v>7169743</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1593,15 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121569687</v>
+        <v>121569689</v>
       </c>
       <c r="B11" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1609,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>646212</v>
+        <v>646095</v>
       </c>
       <c r="R11" t="n">
-        <v>7169717</v>
+        <v>7169705</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1695,37 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121569683</v>
+        <v>121569692</v>
       </c>
       <c r="B12" t="n">
-        <v>74735</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>646201</v>
+        <v>645978</v>
       </c>
       <c r="R12" t="n">
-        <v>7169783</v>
+        <v>7169870</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1797,48 +1742,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133941656</v>
+        <v>121569684</v>
       </c>
       <c r="B13" t="n">
-        <v>83351</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Öravan, Ly lm</t>
+          <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>646189</v>
+        <v>646230</v>
       </c>
       <c r="R13" t="n">
-        <v>7169652</v>
+        <v>7169726</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1862,12 +1807,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1882,60 +1827,60 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Linda Spjut</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Linda Spjut</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133941654</v>
+        <v>121569687</v>
       </c>
       <c r="B14" t="n">
-        <v>83351</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Öravan, Ly lm</t>
+          <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>646177</v>
+        <v>646212</v>
       </c>
       <c r="R14" t="n">
-        <v>7169660</v>
+        <v>7169717</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1959,12 +1904,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1979,60 +1924,60 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Linda Spjut</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Linda Spjut</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133941668</v>
+        <v>121569691</v>
       </c>
       <c r="B15" t="n">
-        <v>91967</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Öravan, Ly lm</t>
+          <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>646255</v>
+        <v>646104</v>
       </c>
       <c r="R15" t="n">
-        <v>7169679</v>
+        <v>7169762</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2056,12 +2001,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2076,60 +2021,60 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Linda Spjut</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Linda Spjut</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133941784</v>
+        <v>121569693</v>
       </c>
       <c r="B16" t="n">
-        <v>83215</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Öravan, Ly lm</t>
+          <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>646177</v>
+        <v>645994</v>
       </c>
       <c r="R16" t="n">
-        <v>7169660</v>
+        <v>7169871</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2153,12 +2098,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2173,22 +2118,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Linda Spjut</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Linda Spjut</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133941669</v>
+        <v>121569683</v>
       </c>
       <c r="B17" t="n">
-        <v>91967</v>
+        <v>83307</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2196,37 +2141,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Öravan, Ly lm</t>
+          <t>Fäboliden, Ly lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>646227</v>
+        <v>646201</v>
       </c>
       <c r="R17" t="n">
-        <v>7169691</v>
+        <v>7169783</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2250,12 +2195,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2270,22 +2215,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Linda Spjut</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Linda Spjut</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133941670</v>
+        <v>133941654</v>
       </c>
       <c r="B18" t="n">
-        <v>91967</v>
+        <v>83358</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2293,21 +2238,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2317,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>646157</v>
+        <v>646177</v>
       </c>
       <c r="R18" t="n">
-        <v>7169752</v>
+        <v>7169660</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2379,10 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133941785</v>
+        <v>133941656</v>
       </c>
       <c r="B19" t="n">
-        <v>83215</v>
+        <v>83358</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2390,21 +2335,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2414,7 +2359,7 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>646205</v>
+        <v>646189</v>
       </c>
       <c r="R19" t="n">
         <v>7169652</v>

--- a/artfynd/A 23221-2026 artfynd.xlsx
+++ b/artfynd/A 23221-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121569685</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121569686</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133941668</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133941669</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133941670</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133941784</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133941785</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121569688</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121569690</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121569689</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121569692</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121569684</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121569687</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121569691</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121569693</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121569683</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133941654</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,8 +2508,33 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133941656</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>